--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E4A818-93AC-4829-8FA5-6540CC403653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF2522A-1837-4FDB-8EF7-84CBD5A2B18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1236" yWindow="1440" windowWidth="13332" windowHeight="10536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -37,14 +37,43 @@
   </si>
   <si>
     <t>Chapter Name</t>
+  </si>
+  <si>
+    <t>Encapsulation &amp; Inheritance</t>
+  </si>
+  <si>
+    <t>Control Statementsl Math &amp; String</t>
+  </si>
+  <si>
+    <t>Classes &amp; Objects</t>
+  </si>
+  <si>
+    <t>Operators, If-Else &amp; Numeber System</t>
+  </si>
+  <si>
+    <t>Data Types, Variables &amp; Input</t>
+  </si>
+  <si>
+    <t>Java Basics</t>
+  </si>
+  <si>
+    <t>Introduction to Java</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -72,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -80,11 +109,53 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -95,6 +166,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A2:D9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A2:D9" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{130595FE-1AE6-4A5D-9097-F87314C83BF8}" name="Page NO." dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{985B9830-8932-4761-8DBE-FFE0C9147423}" name="Date " dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -360,78 +444,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D6"/>
+  <dimension ref="A2:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
         <v>3</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1">
-        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>46152</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1">
-        <v>73</v>
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3">
+        <v>27</v>
       </c>
       <c r="D4" s="2">
-        <v>46153</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C5" s="1">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2">
-        <v>46154</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1"/>
       <c r="C6" s="1">
+        <v>73</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>117</v>
+      </c>
+      <c r="D7" s="2">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
         <v>149</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D8" s="2">
         <v>46155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>175</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF2522A-1837-4FDB-8EF7-84CBD5A2B18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6B0F55-E53A-4E21-93D1-A888FE387759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Classes &amp; Objects</t>
   </si>
   <si>
-    <t>Operators, If-Else &amp; Numeber System</t>
-  </si>
-  <si>
     <t>Data Types, Variables &amp; Input</t>
   </si>
   <si>
@@ -58,6 +55,27 @@
   </si>
   <si>
     <t>Introduction to Java</t>
+  </si>
+  <si>
+    <t>Abstraction and Polymorphism</t>
+  </si>
+  <si>
+    <t>Exception and file Handling</t>
+  </si>
+  <si>
+    <t>collections and generics</t>
+  </si>
+  <si>
+    <t>4&amp;5</t>
+  </si>
+  <si>
+    <t>Operators, If-Else &amp; Number System</t>
+  </si>
+  <si>
+    <t>Java Revision From 10 May 2026</t>
+  </si>
+  <si>
+    <t>Multi threding and Excecutive Services</t>
   </si>
 </sst>
 </file>
@@ -81,12 +99,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -101,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -115,11 +139,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -139,22 +182,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -169,13 +196,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A2:D9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A2:D9" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A4:D15" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{130595FE-1AE6-4A5D-9097-F87314C83BF8}" name="Page NO." dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{985B9830-8932-4761-8DBE-FFE0C9147423}" name="Date " dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{130595FE-1AE6-4A5D-9097-F87314C83BF8}" name="Page NO." dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{985B9830-8932-4761-8DBE-FFE0C9147423}" name="Date " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -444,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D9"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -454,115 +481,176 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3">
         <v>3</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1">
-        <v>53</v>
       </c>
       <c r="D5" s="2">
         <v>46152</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>4</v>
+      <c r="A6" s="3">
+        <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1">
-        <v>73</v>
+        <v>8</v>
+      </c>
+      <c r="C6" s="3">
+        <v>27</v>
       </c>
       <c r="D6" s="2">
-        <v>46153</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2">
-        <v>46154</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
+      <c r="A8" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="D8" s="2">
-        <v>46155</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>117</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>149</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C11" s="1">
         <v>175</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D11" s="2">
         <v>46158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>195</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <v>216</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>235</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1">
+        <v>257</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46162</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6B0F55-E53A-4E21-93D1-A888FE387759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F85004-B372-4C23-B297-E6812480ACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Multi threding and Excecutive Services</t>
+  </si>
+  <si>
+    <t>Thread Priority</t>
+  </si>
+  <si>
+    <t>Introduction to Executer Service</t>
   </si>
 </sst>
 </file>
@@ -196,8 +202,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A4:D15" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D17" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A4:D17" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="2"/>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D15"/>
+  <dimension ref="A2:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -653,6 +659,34 @@
         <v>46162</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1">
+        <v>263</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1">
+        <v>269</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F85004-B372-4C23-B297-E6812480ACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9017A18-8383-43E1-908E-912AE7DB05C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Introduction to Executer Service</t>
+  </si>
+  <si>
+    <t>Functional Programming</t>
   </si>
 </sst>
 </file>
@@ -202,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D17" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A4:D17" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D18" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A4:D18" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="2"/>
@@ -477,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D17"/>
+  <dimension ref="A2:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -687,6 +690,20 @@
         <v>46165</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1">
+        <v>278</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9017A18-8383-43E1-908E-912AE7DB05C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39D7AED-FB7C-4F47-A70A-5CAB439916DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Functional Programming</t>
+  </si>
+  <si>
+    <t>Functional Interfaces</t>
   </si>
 </sst>
 </file>
@@ -205,8 +208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D18" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A4:D18" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}" name="Table1" displayName="Table1" ref="A4:D19" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A4:D19" xr:uid="{0AC1DC6B-9171-4FFE-8540-376901D58DCC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{8F548AFB-71A0-4308-A178-1BA058E19B96}" name="Chapter NO." dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{6A2404E8-B5C9-4B22-9762-60A592CB9AAE}" name="Chapter Name" dataDxfId="2"/>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D18"/>
+  <dimension ref="A2:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -704,6 +707,20 @@
         <v>46166</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1">
+        <v>286</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39D7AED-FB7C-4F47-A70A-5CAB439916DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C068D48F-9425-4521-80BA-8DDF1738975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -88,6 +89,352 @@
   </si>
   <si>
     <t>Functional Interfaces</t>
+  </si>
+  <si>
+    <t>OOPS</t>
+  </si>
+  <si>
+    <t>Encapsulation</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inheritance</t>
+  </si>
+  <si>
+    <t>Polymorphisms</t>
+  </si>
+  <si>
+    <t>Definition in my own words</t>
+  </si>
+  <si>
+    <t>Topic Name</t>
+  </si>
+  <si>
+    <t>Subtopics</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hides data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, varible for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>security purpose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>private</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for variable name . Access them only with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>setters</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> methods.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It tells these </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>things are must to do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . It </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not tells how to do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.It is created by keyword of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Abstract</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and access by keyword of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>extends</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">we can use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>properties of other classes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (parent class) like varibles, by using keyword </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>implement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Many forms: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1)Method overlodding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : same method name different behaviour(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compile time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) . </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2) Method overriding:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> writing our method over parent class method. (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>run time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -137,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +499,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -727,4 +1086,88 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB1AD9-6496-453A-828E-D24A232BA840}">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" customWidth="1"/>
+    <col min="4" max="4" width="50.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B7" s="6"/>
+      <c r="C7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="6"/>
+      <c r="C8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="6"/>
+      <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B3:B9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C068D48F-9425-4521-80BA-8DDF1738975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947D20B7-FE29-4139-9935-13BDECB97955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Topic name &amp; page number" sheetId="1" r:id="rId1"/>
+    <sheet name="Topics Revision" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -43,9 +43,6 @@
     <t>Encapsulation &amp; Inheritance</t>
   </si>
   <si>
-    <t>Control Statementsl Math &amp; String</t>
-  </si>
-  <si>
     <t>Classes &amp; Objects</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Encapsulation</t>
   </si>
   <si>
-    <t>Abstract</t>
-  </si>
-  <si>
     <t>Inheritance</t>
   </si>
   <si>
@@ -435,6 +429,12 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Control Statements Math &amp; String</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
   </si>
 </sst>
 </file>
@@ -853,7 +853,7 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3">
         <v>27</v>
@@ -903,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
         <v>53</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>73</v>
@@ -931,7 +931,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1">
         <v>117</v>
@@ -945,7 +945,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1">
         <v>149</v>
@@ -973,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <v>195</v>
@@ -987,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <v>216</v>
@@ -1001,7 +1001,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
         <v>235</v>
@@ -1015,7 +1015,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>257</v>
@@ -1029,7 +1029,7 @@
         <v>12.4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1">
         <v>263</v>
@@ -1043,7 +1043,7 @@
         <v>12.8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>269</v>
@@ -1057,7 +1057,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1">
         <v>278</v>
@@ -1071,7 +1071,7 @@
         <v>13.4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <v>286</v>
@@ -1100,24 +1100,24 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
@@ -1138,28 +1138,28 @@
     <row r="7" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B7" s="6"/>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="6"/>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" s="6"/>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/Java Revision from 10 May 2026.xlsx
+++ b/Notes/Java Revision from 10 May 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\JAVA\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947D20B7-FE29-4139-9935-13BDECB97955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E696189-ABFF-4D74-AA1F-C116989C84DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Topic name &amp; page number" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Chapter NO.</t>
   </si>
@@ -435,6 +435,77 @@
   </si>
   <si>
     <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It is a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contract</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, it </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>defines what to do not how to do</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Class uses </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>implements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to use </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -502,15 +573,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1090,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DB1AD9-6496-453A-828E-D24A232BA840}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.5546875" customWidth="1"/>
@@ -1110,10 +1181,10 @@
       </c>
     </row>
     <row r="3" spans="2:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1121,45 +1192,53 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B7" s="6"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="6"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
